--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939377</v>
+        <v>119939370</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608954</v>
+        <v>608704</v>
       </c>
       <c r="R8" t="n">
-        <v>6978061</v>
+        <v>6978234</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939370</v>
+        <v>119939374</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608704</v>
+        <v>608677</v>
       </c>
       <c r="R9" t="n">
-        <v>6978234</v>
+        <v>6978123</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939374</v>
+        <v>119939377</v>
       </c>
       <c r="B10" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608677</v>
+        <v>608954</v>
       </c>
       <c r="R10" t="n">
-        <v>6978123</v>
+        <v>6978061</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119939380</v>
+        <v>119939370</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609006</v>
+        <v>608704</v>
       </c>
       <c r="R2" t="n">
-        <v>6978019</v>
+        <v>6978234</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939373</v>
+        <v>119939371</v>
       </c>
       <c r="B3" t="n">
-        <v>86878</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608670</v>
+        <v>608628</v>
       </c>
       <c r="R3" t="n">
-        <v>6978126</v>
+        <v>6978161</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939376</v>
+        <v>119939374</v>
       </c>
       <c r="B4" t="n">
-        <v>86878</v>
+        <v>78560</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608943</v>
+        <v>608677</v>
       </c>
       <c r="R4" t="n">
-        <v>6978081</v>
+        <v>6978123</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939378</v>
+        <v>119939376</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>86878</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608920</v>
+        <v>608943</v>
       </c>
       <c r="R5" t="n">
-        <v>6978064</v>
+        <v>6978081</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119939371</v>
+        <v>119939380</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608628</v>
+        <v>609006</v>
       </c>
       <c r="R6" t="n">
-        <v>6978161</v>
+        <v>6978019</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119939379</v>
+        <v>119939372</v>
       </c>
       <c r="B7" t="n">
-        <v>90527</v>
+        <v>90846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,25 +1267,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609002</v>
+        <v>608663</v>
       </c>
       <c r="R7" t="n">
-        <v>6978016</v>
+        <v>6978146</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939370</v>
+        <v>119939378</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608704</v>
+        <v>608920</v>
       </c>
       <c r="R8" t="n">
-        <v>6978234</v>
+        <v>6978064</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939374</v>
+        <v>119939373</v>
       </c>
       <c r="B9" t="n">
-        <v>78560</v>
+        <v>86878</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608677</v>
+        <v>608670</v>
       </c>
       <c r="R9" t="n">
-        <v>6978123</v>
+        <v>6978126</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939377</v>
+        <v>119939379</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608954</v>
+        <v>609002</v>
       </c>
       <c r="R10" t="n">
-        <v>6978061</v>
+        <v>6978016</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119939372</v>
+        <v>119939377</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1763,13 +1763,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608663</v>
+        <v>608954</v>
       </c>
       <c r="R11" t="n">
-        <v>6978146</v>
+        <v>6978061</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119939370</v>
+        <v>119939377</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608704</v>
+        <v>608954</v>
       </c>
       <c r="R2" t="n">
-        <v>6978234</v>
+        <v>6978061</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939371</v>
+        <v>119939379</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608628</v>
+        <v>609002</v>
       </c>
       <c r="R3" t="n">
-        <v>6978161</v>
+        <v>6978016</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939374</v>
+        <v>119939378</v>
       </c>
       <c r="B4" t="n">
-        <v>78560</v>
+        <v>82305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608677</v>
+        <v>608920</v>
       </c>
       <c r="R4" t="n">
-        <v>6978123</v>
+        <v>6978064</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939376</v>
+        <v>119939374</v>
       </c>
       <c r="B5" t="n">
-        <v>86878</v>
+        <v>78560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608943</v>
+        <v>608677</v>
       </c>
       <c r="R5" t="n">
-        <v>6978081</v>
+        <v>6978123</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119939372</v>
+        <v>119939373</v>
       </c>
       <c r="B7" t="n">
-        <v>90846</v>
+        <v>86878</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608663</v>
+        <v>608670</v>
       </c>
       <c r="R7" t="n">
-        <v>6978146</v>
+        <v>6978126</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939378</v>
+        <v>119939372</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>90846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608920</v>
+        <v>608663</v>
       </c>
       <c r="R8" t="n">
-        <v>6978064</v>
+        <v>6978146</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939373</v>
+        <v>119939370</v>
       </c>
       <c r="B9" t="n">
-        <v>86878</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608670</v>
+        <v>608704</v>
       </c>
       <c r="R9" t="n">
-        <v>6978126</v>
+        <v>6978234</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939379</v>
+        <v>119939376</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>86878</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609002</v>
+        <v>608943</v>
       </c>
       <c r="R10" t="n">
-        <v>6978016</v>
+        <v>6978081</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119939377</v>
+        <v>119939371</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1763,13 +1763,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608954</v>
+        <v>608628</v>
       </c>
       <c r="R11" t="n">
-        <v>6978061</v>
+        <v>6978161</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119939377</v>
+        <v>119939372</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608954</v>
+        <v>608663</v>
       </c>
       <c r="R2" t="n">
-        <v>6978061</v>
+        <v>6978146</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939379</v>
+        <v>119939370</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609002</v>
+        <v>608704</v>
       </c>
       <c r="R3" t="n">
-        <v>6978016</v>
+        <v>6978234</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939378</v>
+        <v>119939380</v>
       </c>
       <c r="B4" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608920</v>
+        <v>609006</v>
       </c>
       <c r="R4" t="n">
-        <v>6978064</v>
+        <v>6978019</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119939380</v>
+        <v>119939373</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>86878</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609006</v>
+        <v>608670</v>
       </c>
       <c r="R6" t="n">
-        <v>6978019</v>
+        <v>6978126</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119939373</v>
+        <v>119939377</v>
       </c>
       <c r="B7" t="n">
-        <v>86878</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608670</v>
+        <v>608954</v>
       </c>
       <c r="R7" t="n">
-        <v>6978126</v>
+        <v>6978061</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939372</v>
+        <v>119939378</v>
       </c>
       <c r="B8" t="n">
-        <v>90846</v>
+        <v>82305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608663</v>
+        <v>608920</v>
       </c>
       <c r="R8" t="n">
-        <v>6978146</v>
+        <v>6978064</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939370</v>
+        <v>119939376</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>86878</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608704</v>
+        <v>608943</v>
       </c>
       <c r="R9" t="n">
-        <v>6978234</v>
+        <v>6978081</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939376</v>
+        <v>119939379</v>
       </c>
       <c r="B10" t="n">
-        <v>86878</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608943</v>
+        <v>609002</v>
       </c>
       <c r="R10" t="n">
-        <v>6978081</v>
+        <v>6978016</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939380</v>
+        <v>119939374</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609006</v>
+        <v>608677</v>
       </c>
       <c r="R4" t="n">
-        <v>6978019</v>
+        <v>6978123</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939374</v>
+        <v>119939380</v>
       </c>
       <c r="B5" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608677</v>
+        <v>609006</v>
       </c>
       <c r="R5" t="n">
-        <v>6978123</v>
+        <v>6978019</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939374</v>
+        <v>119939380</v>
       </c>
       <c r="B4" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608677</v>
+        <v>609006</v>
       </c>
       <c r="R4" t="n">
-        <v>6978123</v>
+        <v>6978019</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939380</v>
+        <v>119939374</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609006</v>
+        <v>608677</v>
       </c>
       <c r="R5" t="n">
-        <v>6978019</v>
+        <v>6978123</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119939372</v>
+        <v>119939370</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608663</v>
+        <v>608704</v>
       </c>
       <c r="R2" t="n">
-        <v>6978146</v>
+        <v>6978234</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939370</v>
+        <v>119939377</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608704</v>
+        <v>608954</v>
       </c>
       <c r="R3" t="n">
-        <v>6978234</v>
+        <v>6978061</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939380</v>
+        <v>119939374</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609006</v>
+        <v>608677</v>
       </c>
       <c r="R4" t="n">
-        <v>6978019</v>
+        <v>6978123</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939374</v>
+        <v>119939376</v>
       </c>
       <c r="B5" t="n">
-        <v>78560</v>
+        <v>86895</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608677</v>
+        <v>608943</v>
       </c>
       <c r="R5" t="n">
-        <v>6978123</v>
+        <v>6978081</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1142,7 @@
         <v>119939373</v>
       </c>
       <c r="B6" t="n">
-        <v>86878</v>
+        <v>86895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119939377</v>
+        <v>119939372</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608954</v>
+        <v>608663</v>
       </c>
       <c r="R7" t="n">
-        <v>6978061</v>
+        <v>6978146</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939378</v>
+        <v>119939379</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>90545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,25 +1383,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608920</v>
+        <v>609002</v>
       </c>
       <c r="R8" t="n">
-        <v>6978064</v>
+        <v>6978016</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939376</v>
+        <v>119939380</v>
       </c>
       <c r="B9" t="n">
-        <v>86878</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608943</v>
+        <v>609006</v>
       </c>
       <c r="R9" t="n">
-        <v>6978081</v>
+        <v>6978019</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939379</v>
+        <v>119939378</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609002</v>
+        <v>608920</v>
       </c>
       <c r="R10" t="n">
-        <v>6978016</v>
+        <v>6978064</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>119939371</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939377</v>
+        <v>119939374</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608954</v>
+        <v>608677</v>
       </c>
       <c r="R3" t="n">
-        <v>6978061</v>
+        <v>6978123</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939374</v>
+        <v>119939376</v>
       </c>
       <c r="B4" t="n">
-        <v>78576</v>
+        <v>86895</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608677</v>
+        <v>608943</v>
       </c>
       <c r="R4" t="n">
-        <v>6978123</v>
+        <v>6978081</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939376</v>
+        <v>119939377</v>
       </c>
       <c r="B5" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608943</v>
+        <v>608954</v>
       </c>
       <c r="R5" t="n">
-        <v>6978081</v>
+        <v>6978061</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119939370</v>
+        <v>119939371</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608704</v>
+        <v>608628</v>
       </c>
       <c r="R2" t="n">
-        <v>6978234</v>
+        <v>6978161</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939374</v>
+        <v>119939370</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608677</v>
+        <v>608704</v>
       </c>
       <c r="R3" t="n">
-        <v>6978123</v>
+        <v>6978234</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939377</v>
+        <v>119939380</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608954</v>
+        <v>609006</v>
       </c>
       <c r="R5" t="n">
-        <v>6978061</v>
+        <v>6978019</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119939373</v>
+        <v>119939378</v>
       </c>
       <c r="B6" t="n">
-        <v>86895</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608670</v>
+        <v>608920</v>
       </c>
       <c r="R6" t="n">
-        <v>6978126</v>
+        <v>6978064</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939379</v>
+        <v>119939374</v>
       </c>
       <c r="B8" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,25 +1383,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609002</v>
+        <v>608677</v>
       </c>
       <c r="R8" t="n">
-        <v>6978016</v>
+        <v>6978123</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939380</v>
+        <v>119939373</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609006</v>
+        <v>608670</v>
       </c>
       <c r="R9" t="n">
-        <v>6978019</v>
+        <v>6978126</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939378</v>
+        <v>119939377</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608920</v>
+        <v>608954</v>
       </c>
       <c r="R10" t="n">
-        <v>6978064</v>
+        <v>6978061</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119939371</v>
+        <v>119939379</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608628</v>
+        <v>609002</v>
       </c>
       <c r="R11" t="n">
-        <v>6978161</v>
+        <v>6978016</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119939371</v>
+        <v>119939372</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608628</v>
+        <v>608663</v>
       </c>
       <c r="R2" t="n">
-        <v>6978161</v>
+        <v>6978146</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939370</v>
+        <v>119939371</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608704</v>
+        <v>608628</v>
       </c>
       <c r="R3" t="n">
-        <v>6978234</v>
+        <v>6978161</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939376</v>
+        <v>119939380</v>
       </c>
       <c r="B4" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608943</v>
+        <v>609006</v>
       </c>
       <c r="R4" t="n">
-        <v>6978081</v>
+        <v>6978019</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939380</v>
+        <v>119939378</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609006</v>
+        <v>608920</v>
       </c>
       <c r="R5" t="n">
-        <v>6978019</v>
+        <v>6978064</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119939378</v>
+        <v>119939373</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608920</v>
+        <v>608670</v>
       </c>
       <c r="R6" t="n">
-        <v>6978064</v>
+        <v>6978126</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119939372</v>
+        <v>119939374</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>78576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608663</v>
+        <v>608677</v>
       </c>
       <c r="R7" t="n">
-        <v>6978146</v>
+        <v>6978123</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939374</v>
+        <v>119939377</v>
       </c>
       <c r="B8" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608677</v>
+        <v>608954</v>
       </c>
       <c r="R8" t="n">
-        <v>6978123</v>
+        <v>6978061</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939373</v>
+        <v>119939370</v>
       </c>
       <c r="B9" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608670</v>
+        <v>608704</v>
       </c>
       <c r="R9" t="n">
-        <v>6978126</v>
+        <v>6978234</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939377</v>
+        <v>119939376</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608954</v>
+        <v>608943</v>
       </c>
       <c r="R10" t="n">
-        <v>6978061</v>
+        <v>6978081</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939371</v>
+        <v>119939377</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608628</v>
+        <v>608954</v>
       </c>
       <c r="R3" t="n">
-        <v>6978161</v>
+        <v>6978061</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939380</v>
+        <v>119939378</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609006</v>
+        <v>608920</v>
       </c>
       <c r="R4" t="n">
-        <v>6978019</v>
+        <v>6978064</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939378</v>
+        <v>119939376</v>
       </c>
       <c r="B5" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608920</v>
+        <v>608943</v>
       </c>
       <c r="R5" t="n">
-        <v>6978064</v>
+        <v>6978081</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119939373</v>
+        <v>119939371</v>
       </c>
       <c r="B6" t="n">
-        <v>86895</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608670</v>
+        <v>608628</v>
       </c>
       <c r="R6" t="n">
-        <v>6978126</v>
+        <v>6978161</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119939374</v>
+        <v>119939380</v>
       </c>
       <c r="B7" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608677</v>
+        <v>609006</v>
       </c>
       <c r="R7" t="n">
-        <v>6978123</v>
+        <v>6978019</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939377</v>
+        <v>119939370</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608954</v>
+        <v>608704</v>
       </c>
       <c r="R8" t="n">
-        <v>6978061</v>
+        <v>6978234</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939370</v>
+        <v>119939373</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608704</v>
+        <v>608670</v>
       </c>
       <c r="R9" t="n">
-        <v>6978234</v>
+        <v>6978126</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939376</v>
+        <v>119939374</v>
       </c>
       <c r="B10" t="n">
-        <v>86895</v>
+        <v>78576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608943</v>
+        <v>608677</v>
       </c>
       <c r="R10" t="n">
-        <v>6978081</v>
+        <v>6978123</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119939372</v>
+        <v>119939377</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608663</v>
+        <v>608954</v>
       </c>
       <c r="R2" t="n">
-        <v>6978146</v>
+        <v>6978061</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939377</v>
+        <v>119939379</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608954</v>
+        <v>609002</v>
       </c>
       <c r="R3" t="n">
-        <v>6978061</v>
+        <v>6978016</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939378</v>
+        <v>119939373</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608920</v>
+        <v>608670</v>
       </c>
       <c r="R4" t="n">
-        <v>6978064</v>
+        <v>6978126</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939376</v>
+        <v>119939372</v>
       </c>
       <c r="B5" t="n">
-        <v>86895</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608943</v>
+        <v>608663</v>
       </c>
       <c r="R5" t="n">
-        <v>6978081</v>
+        <v>6978146</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119939371</v>
+        <v>119939380</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608628</v>
+        <v>609006</v>
       </c>
       <c r="R6" t="n">
-        <v>6978161</v>
+        <v>6978019</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119939380</v>
+        <v>119939376</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609006</v>
+        <v>608943</v>
       </c>
       <c r="R7" t="n">
-        <v>6978019</v>
+        <v>6978081</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939370</v>
+        <v>119939378</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608704</v>
+        <v>608920</v>
       </c>
       <c r="R8" t="n">
-        <v>6978234</v>
+        <v>6978064</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939373</v>
+        <v>119939370</v>
       </c>
       <c r="B9" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608670</v>
+        <v>608704</v>
       </c>
       <c r="R9" t="n">
-        <v>6978126</v>
+        <v>6978234</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939374</v>
+        <v>119939371</v>
       </c>
       <c r="B10" t="n">
-        <v>78576</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608677</v>
+        <v>608628</v>
       </c>
       <c r="R10" t="n">
-        <v>6978123</v>
+        <v>6978161</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119939379</v>
+        <v>119939374</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609002</v>
+        <v>608677</v>
       </c>
       <c r="R11" t="n">
-        <v>6978016</v>
+        <v>6978123</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939379</v>
+        <v>119939376</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>86895</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609002</v>
+        <v>608943</v>
       </c>
       <c r="R3" t="n">
-        <v>6978016</v>
+        <v>6978081</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939373</v>
+        <v>119939372</v>
       </c>
       <c r="B4" t="n">
-        <v>86895</v>
+        <v>90864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608670</v>
+        <v>608663</v>
       </c>
       <c r="R4" t="n">
-        <v>6978126</v>
+        <v>6978146</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939372</v>
+        <v>119939371</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608663</v>
+        <v>608628</v>
       </c>
       <c r="R5" t="n">
-        <v>6978146</v>
+        <v>6978161</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119939380</v>
+        <v>119939374</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609006</v>
+        <v>608677</v>
       </c>
       <c r="R6" t="n">
-        <v>6978019</v>
+        <v>6978123</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119939376</v>
+        <v>119939378</v>
       </c>
       <c r="B7" t="n">
-        <v>86895</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608943</v>
+        <v>608920</v>
       </c>
       <c r="R7" t="n">
-        <v>6978081</v>
+        <v>6978064</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939378</v>
+        <v>119939380</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608920</v>
+        <v>609006</v>
       </c>
       <c r="R8" t="n">
-        <v>6978064</v>
+        <v>6978019</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939370</v>
+        <v>119939379</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,25 +1499,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608704</v>
+        <v>609002</v>
       </c>
       <c r="R9" t="n">
-        <v>6978234</v>
+        <v>6978016</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939371</v>
+        <v>119939370</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608628</v>
+        <v>608704</v>
       </c>
       <c r="R10" t="n">
-        <v>6978161</v>
+        <v>6978234</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119939374</v>
+        <v>119939373</v>
       </c>
       <c r="B11" t="n">
-        <v>78576</v>
+        <v>86895</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608677</v>
+        <v>608670</v>
       </c>
       <c r="R11" t="n">
-        <v>6978123</v>
+        <v>6978126</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54049-2023 artfynd.xlsx
+++ b/artfynd/A 54049-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119939377</v>
+        <v>119939379</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608954</v>
+        <v>609002</v>
       </c>
       <c r="R2" t="n">
-        <v>6978061</v>
+        <v>6978016</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119939376</v>
+        <v>119939371</v>
       </c>
       <c r="B3" t="n">
-        <v>86895</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608943</v>
+        <v>608628</v>
       </c>
       <c r="R3" t="n">
-        <v>6978081</v>
+        <v>6978161</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119939372</v>
+        <v>119939376</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>86895</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608663</v>
+        <v>608943</v>
       </c>
       <c r="R4" t="n">
-        <v>6978146</v>
+        <v>6978081</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119939371</v>
+        <v>119939377</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608628</v>
+        <v>608954</v>
       </c>
       <c r="R5" t="n">
-        <v>6978161</v>
+        <v>6978061</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119939374</v>
+        <v>119939372</v>
       </c>
       <c r="B6" t="n">
-        <v>78576</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608677</v>
+        <v>608663</v>
       </c>
       <c r="R6" t="n">
-        <v>6978123</v>
+        <v>6978146</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119939380</v>
+        <v>119939373</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609006</v>
+        <v>608670</v>
       </c>
       <c r="R8" t="n">
-        <v>6978019</v>
+        <v>6978126</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119939379</v>
+        <v>119939370</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,25 +1499,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609002</v>
+        <v>608704</v>
       </c>
       <c r="R9" t="n">
-        <v>6978016</v>
+        <v>6978234</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119939370</v>
+        <v>119939374</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608704</v>
+        <v>608677</v>
       </c>
       <c r="R10" t="n">
-        <v>6978234</v>
+        <v>6978123</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119939373</v>
+        <v>119939380</v>
       </c>
       <c r="B11" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608670</v>
+        <v>609006</v>
       </c>
       <c r="R11" t="n">
-        <v>6978126</v>
+        <v>6978019</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
